--- a/Pesquisa_Operacional_07_10_2026.xlsx
+++ b/Pesquisa_Operacional_07_10_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C3C51-7DF9-4E90-B9BE-1B887BCFBD96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D97136-87B6-4738-96F8-C1C8AA175831}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{8D6C0FA3-C012-4463-B83B-7B6D56B3562A}"/>
   </bookViews>
@@ -38,7 +38,7 @@
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'EX1'!$I$7:$I$11</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'EX2'!$L$9:$L$14</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'EX3'!$F$27:$F$34</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'EX3'!$F$27:$F$31</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'EX3'!$F$32:$F$34</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
@@ -60,7 +60,7 @@
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
@@ -79,7 +79,7 @@
     <definedName name="solver_rel2" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'EX1'!$J$7:$J$11</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'EX2'!$M$9:$M$14</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'EX3'!$G$27:$G$34</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'EX3'!$G$27:$G$31</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">'EX3'!$G$32:$G$34</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
@@ -341,6 +341,203 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>24466</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5FBE972-4F61-4A2E-8235-8BD18335D59F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3648074" y="95250"/>
+          <a:ext cx="5029201" cy="3005791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>126926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>554903</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19768</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAFF3451-7BC5-488B-BB06-DD42584299D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9220200" y="307901"/>
+          <a:ext cx="8279678" cy="2426492"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>162796</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>561923</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FADEC77D-9E03-46D5-A61B-5E06C6285E92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9220199" y="3239371"/>
+          <a:ext cx="8286699" cy="2437529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Seta: para Baixo 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46801FFE-4781-49E5-99E6-F6E62052FA5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9753600" y="2800350"/>
+          <a:ext cx="361950" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1194,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K5" s="4"/>
       <c r="N5" s="4"/>
@@ -1210,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -1232,7 +1429,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="5">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -1246,10 +1443,10 @@
         <v>33</v>
       </c>
       <c r="B9" s="5">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C9" s="5">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D9" s="5">
         <v>0</v>
@@ -1335,7 +1532,7 @@
       </c>
       <c r="G24" s="3">
         <f>SUMPRODUCT(B5:D9,B10:D14)</f>
-        <v>0</v>
+        <v>884000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -1356,12 +1553,18 @@
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
       <c r="F27" s="3">
         <f>SUM(B5:D5)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G27" s="2">
         <v>2000</v>
@@ -1371,12 +1574,18 @@
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
       <c r="F28" s="3">
-        <f t="shared" ref="F28:F31" si="0">SUM(B6:D6)</f>
-        <v>0</v>
+        <f>SUM(B6:D6)</f>
+        <v>3000</v>
       </c>
       <c r="G28" s="2">
         <v>3000</v>
@@ -1386,11 +1595,17 @@
       <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
       <c r="F29" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F28:F31" si="0">SUM(B7:D7)</f>
         <v>0</v>
       </c>
       <c r="G29" s="2">
@@ -1401,12 +1616,18 @@
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
       <c r="F30" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G30" s="2">
         <v>3000</v>
@@ -1416,12 +1637,18 @@
       <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="B31" s="2">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G31" s="2">
         <v>5000</v>
@@ -1431,12 +1658,18 @@
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
       <c r="F32" s="3">
         <f>SUM(B5:B9)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G32" s="2">
         <v>5000</v>
@@ -1446,12 +1679,18 @@
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="B33" s="2">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
       <c r="F33" s="3">
         <f>SUM(C5:C9)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G33" s="2">
         <v>3000</v>
@@ -1461,12 +1700,18 @@
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
       <c r="F34" s="3">
-        <f>SUM(D5:D9)</f>
-        <v>0</v>
+        <f>SUM(D5:D7)</f>
+        <v>4000</v>
       </c>
       <c r="G34" s="2">
         <v>4000</v>
@@ -1478,5 +1723,6 @@
     <mergeCell ref="A3:D3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>